--- a/Comprehensive Game Export and Analysis.xlsx
+++ b/Comprehensive Game Export and Analysis.xlsx
@@ -1,20 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deandraper/Documents/Development/Digital Board Gamer/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A275A9AD-E98C-D946-825B-0D1C08388824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="600" windowWidth="44800" windowHeight="24600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Comprehensive Game Export and A" sheetId="1" r:id="rId5"/>
+    <sheet name="Comprehensive Game Export and A" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comprehensive Game Export and A'!$A$1:$J$112</definedName>
+  </definedNames>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="326">
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="322">
   <si>
     <t>Game Title</t>
   </si>
@@ -853,9 +862,6 @@
     <t>Race for the Galaxy</t>
   </si>
   <si>
-    <t>8.5 / 10</t>
-  </si>
-  <si>
     <t>Seasons</t>
   </si>
   <si>
@@ -865,9 +871,6 @@
     <t>Stone Age</t>
   </si>
   <si>
-    <t>8.0 / 10</t>
-  </si>
-  <si>
     <t>Early Review</t>
   </si>
   <si>
@@ -883,9 +886,6 @@
     <t>Hanabi</t>
   </si>
   <si>
-    <t>7.5 / 10</t>
-  </si>
-  <si>
     <t>Co-Op Spotlight</t>
   </si>
   <si>
@@ -910,9 +910,6 @@
     <t>Star Realms</t>
   </si>
   <si>
-    <t>9.0 / 10</t>
-  </si>
-  <si>
     <t>App Spotlight</t>
   </si>
   <si>
@@ -989,32 +986,50 @@
   </si>
   <si>
     <t>Demonstrated how the digital 3D train made the programming mechanics much easier to visualize.</t>
+  </si>
+  <si>
+    <t>Year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="166" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+  </numFmts>
+  <fonts count="5">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF1F1F1F"/>
       <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1022,46 +1037,50 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1251,2677 +1270,2696 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J112"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="4" max="4" width="20.0"/>
-    <col customWidth="1" min="7" max="7" width="19.13"/>
-    <col customWidth="1" min="8" max="9" width="21.38"/>
-    <col customWidth="1" min="10" max="10" width="69.5"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" style="6"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="7" max="7" width="19.1640625" customWidth="1"/>
+    <col min="8" max="9" width="21.33203125" customWidth="1"/>
+    <col min="10" max="10" width="69.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A2" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1">
-        <v>2026.0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A3" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1">
-        <v>2026.0</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>13</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A4" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1">
-        <v>2026.0</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A5" s="1">
+        <v>2026</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1">
-        <v>2026.0</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1">
-        <v>2025.0</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="4">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="1">
-        <v>10.0</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="1">
-        <v>2025.0</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1">
       <c r="A7" s="1">
-        <v>2025.0</v>
+        <v>2023</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="1">
-        <v>9.5</v>
+        <v>108</v>
+      </c>
+      <c r="C7" s="4">
+        <v>10</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1">
-        <v>2025.0</v>
+        <v>2023</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>28</v>
+        <v>109</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1">
       <c r="A8" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="1">
-        <v>9.0</v>
+        <v>60</v>
+      </c>
+      <c r="C8" s="4">
+        <v>10</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="F8" s="1">
-        <v>2025.0</v>
+        <v>2024</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1">
       <c r="A9" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="1">
-        <v>8.5</v>
+        <v>64</v>
+      </c>
+      <c r="C9" s="4">
+        <v>9.5</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="1">
-        <v>2025.0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="1" t="s">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1">
       <c r="A10" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="1">
-        <v>8.0</v>
+        <v>67</v>
+      </c>
+      <c r="C10" s="4">
+        <v>9.5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F10" s="1">
-        <v>2025.0</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1">
       <c r="A11" s="1">
-        <v>2025.0</v>
+        <v>2024</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="C11" s="1">
-        <v>8.0</v>
+        <v>76</v>
+      </c>
+      <c r="C11" s="4">
+        <v>9.5</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1">
-        <v>2025.0</v>
+        <v>2024</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1">
       <c r="A12" s="1">
-        <v>2025.0</v>
+        <v>2021</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="1">
-        <v>7.5</v>
+        <v>154</v>
+      </c>
+      <c r="C12" s="4">
+        <v>9.5</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F12" s="1">
-        <v>2025.0</v>
+        <v>2021</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>32</v>
+        <v>155</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.75" customHeight="1">
       <c r="A13" s="1">
-        <v>2025.0</v>
+        <v>2020</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C13" s="1">
-        <v>9.0</v>
+        <v>173</v>
+      </c>
+      <c r="C13" s="4">
+        <v>9.5</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="F13" s="1">
-        <v>2025.0</v>
+        <v>2020</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.75" customHeight="1">
       <c r="A14" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" s="1">
-        <v>8.5</v>
+        <v>25</v>
+      </c>
+      <c r="C14" s="4">
+        <v>9.5</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.75" customHeight="1">
       <c r="A15" s="1">
-        <v>2025.0</v>
+        <v>2022</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="1">
-        <v>8.0</v>
+        <v>131</v>
+      </c>
+      <c r="C15" s="4">
+        <v>9.5</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="F15" s="1">
-        <v>2025.0</v>
+        <v>2022</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.75" customHeight="1">
       <c r="A16" s="1">
-        <v>2025.0</v>
+        <v>2024</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10.0</v>
+        <v>88</v>
+      </c>
+      <c r="C16" s="4">
+        <v>9.5</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="1">
-        <v>2024.0</v>
-      </c>
+        <v>38</v>
+      </c>
+      <c r="F16" s="1"/>
       <c r="G16" s="1" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.75" customHeight="1">
       <c r="A17" s="1">
-        <v>2025.0</v>
+        <v>2021</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="C17" s="1">
-        <v>9.5</v>
+        <v>166</v>
+      </c>
+      <c r="C17" s="4">
+        <v>9</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="1" t="s">
-        <v>66</v>
+        <v>168</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.75" customHeight="1">
       <c r="A18" s="1">
-        <v>2025.0</v>
+        <v>2022</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="1">
-        <v>9.5</v>
+        <v>125</v>
+      </c>
+      <c r="C18" s="4">
+        <v>9</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>12</v>
+        <v>22</v>
+      </c>
+      <c r="F18" s="1">
+        <v>2022</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>69</v>
+        <v>126</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.75" customHeight="1">
       <c r="A19" s="1">
-        <v>2025.0</v>
+        <v>2021</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="C19" s="1">
-        <v>8.0</v>
+        <v>157</v>
+      </c>
+      <c r="C19" s="4">
+        <v>9</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>72</v>
+        <v>11</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>12</v>
+        <v>26</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2021</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>40</v>
+        <v>158</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.75" customHeight="1">
       <c r="A20" s="1">
-        <v>2025.0</v>
+        <v>2025</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="1">
-        <v>8.5</v>
+        <v>29</v>
+      </c>
+      <c r="C20" s="4">
+        <v>9</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="F20" s="1">
+        <v>2025</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.75" customHeight="1">
       <c r="A21" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" s="1">
-        <v>9.5</v>
+        <v>82</v>
+      </c>
+      <c r="C21" s="4">
+        <v>9</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F21" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.75" customHeight="1">
       <c r="A22" s="1">
-        <v>2024.0</v>
+        <v>2023</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" s="1">
-        <v>8.5</v>
+        <v>115</v>
+      </c>
+      <c r="C22" s="4">
+        <v>9</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F22" s="1">
-        <v>2024.0</v>
+        <v>2023</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.75" customHeight="1">
       <c r="A23" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" s="1">
-        <v>9.0</v>
+        <v>85</v>
+      </c>
+      <c r="C23" s="4">
+        <v>9</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F23" s="1">
-        <v>2024.0</v>
+        <v>2024</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.75" customHeight="1">
       <c r="A24" s="1">
-        <v>2024.0</v>
+        <v>2022</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" s="1">
-        <v>9.0</v>
+        <v>134</v>
+      </c>
+      <c r="C24" s="4">
+        <v>9</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F24" s="1">
-        <v>2024.0</v>
+        <v>2022</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>87</v>
+        <v>135</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.75" customHeight="1">
       <c r="A25" s="1">
-        <v>2024.0</v>
+        <v>2020</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="C25" s="1">
-        <v>9.5</v>
+        <v>182</v>
+      </c>
+      <c r="C25" s="4">
+        <v>9</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
+      </c>
+      <c r="F25" s="1">
+        <v>2020</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.75" customHeight="1">
       <c r="A26" s="1">
-        <v>2024.0</v>
+        <v>2022</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" s="1">
-        <v>8.5</v>
+        <v>137</v>
+      </c>
+      <c r="C26" s="4">
+        <v>9</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="F26" s="1">
+        <v>2022</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.75" customHeight="1">
       <c r="A27" s="1">
-        <v>2024.0</v>
+        <v>2025</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="C27" s="1">
-        <v>8.0</v>
+        <v>48</v>
+      </c>
+      <c r="C27" s="4">
+        <v>9</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>12</v>
+        <v>49</v>
+      </c>
+      <c r="F27" s="1">
+        <v>2025</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1">
-        <v>2024.0</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="H28" s="1"/>
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A28" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="C28" s="5">
+        <v>9</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>295</v>
+      </c>
       <c r="I28" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1">
-        <v>2024.0</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C29" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H29" s="1"/>
+        <v>0</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A29" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="C29" s="5">
+        <v>9</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>301</v>
+      </c>
       <c r="I29" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.75" customHeight="1">
       <c r="A30" s="1">
-        <v>2024.0</v>
+        <v>2025</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="1">
-        <v>7.5</v>
+        <v>73</v>
+      </c>
+      <c r="C30" s="4">
+        <v>8.5</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.75" customHeight="1">
       <c r="A31" s="1">
-        <v>2024.0</v>
+        <v>2022</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31" s="1">
-        <v>2024.0</v>
-      </c>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1" t="s">
-        <v>7</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="C31" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H31" s="1"/>
       <c r="I31" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.75" customHeight="1">
       <c r="A32" s="1">
-        <v>2023.0</v>
+        <v>2024</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="1">
-        <v>10.0</v>
+        <v>79</v>
+      </c>
+      <c r="C32" s="4">
+        <v>8.5</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F32" s="1">
-        <v>2023.0</v>
+        <v>2024</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J32" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A33" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1">
-        <v>2023.0</v>
-      </c>
-      <c r="B33" s="1" t="s">
+      <c r="C33" s="4">
+        <v>8.5</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C33" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F33" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>113</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="1">
-        <v>2023.0</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>114</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.75" customHeight="1">
       <c r="A34" s="1">
-        <v>2023.0</v>
+        <v>2022</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C34" s="1">
-        <v>9.0</v>
+        <v>128</v>
+      </c>
+      <c r="C34" s="4">
+        <v>8.5</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="F34" s="1">
-        <v>2023.0</v>
+        <v>2022</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.75" customHeight="1">
       <c r="A35" s="1">
-        <v>2023.0</v>
+        <v>2020</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="C35" s="1">
-        <v>8.0</v>
+        <v>176</v>
+      </c>
+      <c r="C35" s="4">
+        <v>8.5</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="F35" s="1">
-        <v>2023.0</v>
+        <v>2020</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="36">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.75" customHeight="1">
       <c r="A36" s="1">
-        <v>2023.0</v>
+        <v>2020</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C36" s="1">
-        <v>7.5</v>
+        <v>179</v>
+      </c>
+      <c r="C36" s="4">
+        <v>8.5</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>123</v>
+        <v>11</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>12</v>
+        <v>30</v>
+      </c>
+      <c r="F36" s="1">
+        <v>2020</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="15.75" customHeight="1">
       <c r="A37" s="1">
-        <v>2022.0</v>
+        <v>2025</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="C37" s="1">
-        <v>9.0</v>
+        <v>33</v>
+      </c>
+      <c r="C37" s="4">
+        <v>8.5</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="F37" s="1">
-        <v>2022.0</v>
+        <v>2025</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>127</v>
+        <v>35</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="38">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="15.75" customHeight="1">
       <c r="A38" s="1">
-        <v>2022.0</v>
+        <v>2021</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="C38" s="1">
+        <v>160</v>
+      </c>
+      <c r="C38" s="4">
         <v>8.5</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="F38" s="1">
-        <v>2022.0</v>
+        <v>2021</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.75" customHeight="1">
       <c r="A39" s="1">
-        <v>2022.0</v>
+        <v>2024</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="C39" s="1">
-        <v>9.5</v>
+        <v>91</v>
+      </c>
+      <c r="C39" s="4">
+        <v>8.5</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2022.0</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
-        <v>133</v>
+        <v>92</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="40">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="15.75" customHeight="1">
       <c r="A40" s="1">
-        <v>2022.0</v>
+        <v>2025</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="C40" s="1">
-        <v>9.0</v>
+        <v>52</v>
+      </c>
+      <c r="C40" s="4">
+        <v>8.5</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="F40" s="1">
-        <v>2022.0</v>
+        <v>2025</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>136</v>
+        <v>54</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="15.75" customHeight="1">
       <c r="A41" s="1">
-        <v>2022.0</v>
+        <v>2021</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="C41" s="1">
-        <v>9.0</v>
+        <v>163</v>
+      </c>
+      <c r="C41" s="4">
+        <v>8.5</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="F41" s="1">
-        <v>2022.0</v>
+        <v>2021</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>130</v>
+        <v>164</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="C42" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F42" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H42" s="1"/>
+        <v>165</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A42" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="C42" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="I42" s="1" t="b">
         <v>1</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="C43" s="1">
-        <v>7.5</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F43" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H43" s="1"/>
+      <c r="J42" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A43" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C43" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>304</v>
+      </c>
       <c r="I43" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1">
-        <v>2022.0</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="C44" s="1">
+        <v>0</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A44" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="C44" s="5">
         <v>8.5</v>
       </c>
-      <c r="D44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="H44" s="1"/>
+      <c r="H44" s="3" t="s">
+        <v>307</v>
+      </c>
       <c r="I44" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="45">
+        <v>0</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="15.75" customHeight="1">
       <c r="A45" s="1">
-        <v>2022.0</v>
+        <v>2025</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="C45" s="1">
-        <v>8.0</v>
+        <v>70</v>
+      </c>
+      <c r="C45" s="4">
+        <v>8</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
       <c r="G45" s="1" t="s">
-        <v>150</v>
+        <v>39</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="46">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="15.75" customHeight="1">
       <c r="A46" s="1">
-        <v>2022.0</v>
+        <v>2022</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="C46" s="1">
-        <v>8.0</v>
+        <v>148</v>
+      </c>
+      <c r="C46" s="4">
+        <v>8</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>12</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
       <c r="G46" s="1" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="15.75" customHeight="1">
       <c r="A47" s="1">
-        <v>2021.0</v>
+        <v>2022</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="C47" s="1">
-        <v>9.5</v>
+        <v>151</v>
+      </c>
+      <c r="C47" s="4">
+        <v>8</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2021.0</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="E47" s="1"/>
+      <c r="F47" s="1"/>
       <c r="G47" s="1" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="15.75" customHeight="1">
       <c r="A48" s="1">
-        <v>2021.0</v>
+        <v>2021</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="C48" s="1">
-        <v>9.0</v>
+        <v>170</v>
+      </c>
+      <c r="C48" s="4">
+        <v>8</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" s="1">
-        <v>2021.0</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
       <c r="G48" s="1" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="15.75" customHeight="1">
       <c r="A49" s="1">
-        <v>2021.0</v>
+        <v>2025</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="C49" s="1">
-        <v>8.5</v>
+        <v>56</v>
+      </c>
+      <c r="C49" s="4">
+        <v>8</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="F49" s="1">
-        <v>2021.0</v>
+        <v>2025</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>162</v>
+        <v>58</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="15.75" customHeight="1">
       <c r="A50" s="1">
-        <v>2021.0</v>
+        <v>2023</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="C50" s="1">
-        <v>8.5</v>
+        <v>118</v>
+      </c>
+      <c r="C50" s="4">
+        <v>8</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>12</v>
+        <v>112</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F50" s="1">
-        <v>2021.0</v>
+        <v>2023</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>165</v>
+        <v>119</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="51">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="15.75" customHeight="1">
       <c r="A51" s="1">
-        <v>2021.0</v>
+        <v>2025</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="C51" s="1">
-        <v>9.0</v>
+        <v>37</v>
+      </c>
+      <c r="C51" s="4">
+        <v>8</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>12</v>
+        <v>38</v>
+      </c>
+      <c r="F51" s="1">
+        <v>2025</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>169</v>
+        <v>39</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J51" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="52">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="15.75" customHeight="1">
       <c r="A52" s="1">
-        <v>2021.0</v>
+        <v>2025</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="C52" s="1">
-        <v>8.0</v>
+        <v>41</v>
+      </c>
+      <c r="C52" s="4">
+        <v>8</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>168</v>
+        <v>11</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="1" t="s">
-        <v>12</v>
+        <v>42</v>
+      </c>
+      <c r="F52" s="1">
+        <v>2025</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>172</v>
+        <v>43</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="53">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="15.75" customHeight="1">
       <c r="A53" s="1">
-        <v>2020.0</v>
+        <v>2022</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="C53" s="1">
-        <v>9.5</v>
+        <v>139</v>
+      </c>
+      <c r="C53" s="4">
+        <v>8</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="F53" s="1">
-        <v>2020.0</v>
+        <v>2022</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="54">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="15.75" customHeight="1">
       <c r="A54" s="1">
-        <v>2020.0</v>
+        <v>2024</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="C54" s="1">
-        <v>8.5</v>
+        <v>94</v>
+      </c>
+      <c r="C54" s="4">
+        <v>8</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F54" s="1">
-        <v>2020.0</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1" t="b">
         <v>1</v>
       </c>
       <c r="J54" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1">
-        <v>2020.0</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="C55" s="1">
-        <v>8.5</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A55" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C55" s="5">
+        <v>8</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="I55" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A56" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C56" s="5">
+        <v>8</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="I56" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A57" s="2">
+        <v>2018</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C57" s="5">
+        <v>8</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="I57" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A58" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="4">
+        <v>8</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A59" s="1">
+        <v>2023</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C59" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A60" s="1">
+        <v>2025</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C60" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F60" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G60" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="F55" s="1">
-        <v>2020.0</v>
-      </c>
-      <c r="G55" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J55" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1">
-        <v>2020.0</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C56" s="1">
-        <v>9.0</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F56" s="1">
-        <v>2020.0</v>
-      </c>
-      <c r="G56" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J56" s="1" t="s">
+      <c r="H60" s="1"/>
+      <c r="I60" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A61" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C61" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A62" s="1">
+        <v>2022</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F62" s="1">
+        <v>2022</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" s="1" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A63" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C63" s="4">
+        <v>7.5</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="15.75" customHeight="1">
+      <c r="A64" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="C64" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="I64" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A65" s="1">
+        <v>2024</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F65" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I65" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A66" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B66" s="2" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>2026.0</v>
-      </c>
-      <c r="B57" s="2" t="s">
+      <c r="C66"/>
+      <c r="H66" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="I66" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J66" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I57" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J57" s="3" t="s">
+    </row>
+    <row r="67" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A67" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B67" s="2" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="2">
-        <v>2026.0</v>
-      </c>
-      <c r="B58" s="2" t="s">
+      <c r="C67"/>
+      <c r="H67" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="I67" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J67" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="I58" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J58" s="3" t="s">
+    </row>
+    <row r="68" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A68" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B68" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>2026.0</v>
-      </c>
-      <c r="B59" s="2" t="s">
+      <c r="C68"/>
+      <c r="H68" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="I68" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J68" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="I59" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J59" s="3" t="s">
+    </row>
+    <row r="69" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A69" s="2">
+        <v>2026</v>
+      </c>
+      <c r="B69" s="2" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>2026.0</v>
-      </c>
-      <c r="B60" s="2" t="s">
+      <c r="C69"/>
+      <c r="H69" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="I69" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J69" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I60" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J60" s="3" t="s">
+    </row>
+    <row r="70" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A70" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B70" s="2" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B61" s="2" t="s">
+      <c r="C70"/>
+      <c r="H70" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="I70" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J70" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="I61" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J61" s="3" t="s">
+    </row>
+    <row r="71" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A71" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B71" s="2" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B62" s="2" t="s">
+      <c r="C71"/>
+      <c r="H71" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="I71" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J71" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="I62" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J62" s="3" t="s">
+    </row>
+    <row r="72" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A72" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B63" s="2" t="s">
+      <c r="C72"/>
+      <c r="H72" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="I72" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J72" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I63" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J63" s="3" t="s">
+    </row>
+    <row r="73" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A73" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B64" s="2" t="s">
+      <c r="C73"/>
+      <c r="H73" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J73" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="H64" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I64" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J64" s="3" t="s">
+    </row>
+    <row r="74" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A74" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B74" s="2" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B65" s="2" t="s">
+      <c r="C74"/>
+      <c r="H74" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="I74" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J74" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="I65" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J65" s="3" t="s">
+    </row>
+    <row r="75" spans="1:10" ht="15.75" hidden="1" customHeight="1">
+      <c r="A75" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B75" s="2" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B66" s="2" t="s">
+      <c r="C75"/>
+      <c r="H75" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="I75" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J75" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I66" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J66" s="3" t="s">
+    </row>
+    <row r="76" spans="1:10" ht="13" hidden="1">
+      <c r="A76" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B76" s="2" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B67" s="2" t="s">
+      <c r="C76"/>
+      <c r="H76" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J76" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H67" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I67" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J67" s="3" t="s">
+    </row>
+    <row r="77" spans="1:10" ht="13" hidden="1">
+      <c r="A77" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B77" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B68" s="2" t="s">
+      <c r="C77"/>
+      <c r="H77" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="I77" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J77" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="I68" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J68" s="3" t="s">
+    </row>
+    <row r="78" spans="1:10" ht="13" hidden="1">
+      <c r="A78" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B78" s="2" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B69" s="2" t="s">
+      <c r="C78"/>
+      <c r="H78" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="I78" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J78" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="I69" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J69" s="3" t="s">
+    </row>
+    <row r="79" spans="1:10" ht="13" hidden="1">
+      <c r="A79" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B70" s="2" t="s">
+      <c r="C79"/>
+      <c r="H79" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="I79" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J79" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="I70" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J70" s="3" t="s">
+    </row>
+    <row r="80" spans="1:10" ht="13" hidden="1">
+      <c r="A80" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B71" s="2" t="s">
+      <c r="C80"/>
+      <c r="H80" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I80" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" ht="13" hidden="1">
+      <c r="A81" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I71" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B72" s="2" t="s">
+      <c r="C81"/>
+      <c r="H81" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="I81" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J81" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I72" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J72" s="3" t="s">
+    </row>
+    <row r="82" spans="1:10" ht="13" hidden="1">
+      <c r="A82" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B73" s="2" t="s">
+      <c r="C82"/>
+      <c r="H82" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I82" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J82" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="H73" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I73" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J73" s="3" t="s">
+    </row>
+    <row r="83" spans="1:10" ht="13" hidden="1">
+      <c r="A83" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B74" s="2" t="s">
+      <c r="C83"/>
+      <c r="H83" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I83" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J83" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I74" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J74" s="3" t="s">
+    </row>
+    <row r="84" spans="1:10" ht="13" hidden="1">
+      <c r="A84" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>232</v>
       </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B75" s="2" t="s">
+      <c r="C84"/>
+      <c r="H84" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I84" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J84" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I75" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J75" s="3" t="s">
+    </row>
+    <row r="85" spans="1:10" ht="13" hidden="1">
+      <c r="A85" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B76" s="2" t="s">
+      <c r="C85"/>
+      <c r="H85" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I85" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="13" hidden="1">
+      <c r="A86" s="2">
+        <v>2025</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I76" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2">
-        <v>2025.0</v>
-      </c>
-      <c r="B77" s="2" t="s">
+      <c r="C86"/>
+      <c r="H86" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I86" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="13" hidden="1">
+      <c r="A87" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I77" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2">
-        <v>2024.0</v>
-      </c>
-      <c r="B78" s="2" t="s">
+      <c r="C87"/>
+      <c r="H87" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="I87" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J87" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="I78" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J78" s="3" t="s">
+    </row>
+    <row r="88" spans="1:10" ht="13" hidden="1">
+      <c r="A88" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2">
-        <v>2024.0</v>
-      </c>
-      <c r="B79" s="2" t="s">
+      <c r="C88"/>
+      <c r="H88" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I88" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I79" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J79" s="3" t="s">
+    </row>
+    <row r="89" spans="1:10" ht="13" hidden="1">
+      <c r="A89" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2">
-        <v>2024.0</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="C89"/>
+      <c r="H89" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I89" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J89" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I80" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J80" s="3" t="s">
+    </row>
+    <row r="90" spans="1:10" ht="13" hidden="1">
+      <c r="A90" s="2">
+        <v>2024</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2">
-        <v>2024.0</v>
-      </c>
-      <c r="B81" s="2" t="s">
+      <c r="C90"/>
+      <c r="H90" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H81" s="3" t="s">
+      <c r="I90" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J90" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="I81" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J81" s="3" t="s">
+    </row>
+    <row r="91" spans="1:10" ht="13" hidden="1">
+      <c r="A91" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="2">
-        <v>2023.0</v>
-      </c>
-      <c r="B82" s="2" t="s">
+      <c r="C91"/>
+      <c r="H91" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H82" s="3" t="s">
+      <c r="I91" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J91" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I82" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J82" s="3" t="s">
+    </row>
+    <row r="92" spans="1:10" ht="13" hidden="1">
+      <c r="A92" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2">
-        <v>2023.0</v>
-      </c>
-      <c r="B83" s="2" t="s">
+      <c r="C92"/>
+      <c r="H92" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="I92" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J92" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="I83" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J83" s="3" t="s">
+    </row>
+    <row r="93" spans="1:10" ht="13" hidden="1">
+      <c r="A93" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B93" s="2" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>2023.0</v>
-      </c>
-      <c r="B84" s="2" t="s">
+      <c r="C93"/>
+      <c r="H93" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I93" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J93" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I84" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J84" s="3" t="s">
+    </row>
+    <row r="94" spans="1:10" ht="13" hidden="1">
+      <c r="A94" s="2">
+        <v>2023</v>
+      </c>
+      <c r="B94" s="2" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>2023.0</v>
-      </c>
-      <c r="B85" s="2" t="s">
+      <c r="C94"/>
+      <c r="H94" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="I94" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J94" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I85" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J85" s="3" t="s">
+    </row>
+    <row r="95" spans="1:10" ht="13" hidden="1">
+      <c r="A95" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B95" s="2" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>2022.0</v>
-      </c>
-      <c r="B86" s="2" t="s">
+      <c r="C95"/>
+      <c r="H95" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H86" s="3" t="s">
+      <c r="I95" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J95" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I86" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J86" s="3" t="s">
+    </row>
+    <row r="96" spans="1:10" ht="13" hidden="1">
+      <c r="A96" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B96" s="2" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>2022.0</v>
-      </c>
-      <c r="B87" s="2" t="s">
+      <c r="C96"/>
+      <c r="H96" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="H87" s="3" t="s">
+      <c r="I96" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J96" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="I87" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J87" s="3" t="s">
+    </row>
+    <row r="97" spans="1:10" ht="13" hidden="1">
+      <c r="A97" s="2">
+        <v>2022</v>
+      </c>
+      <c r="B97" s="2" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>2022.0</v>
-      </c>
-      <c r="B88" s="2" t="s">
+      <c r="C97"/>
+      <c r="H97" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I97" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J97" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H88" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I88" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J88" s="3" t="s">
+    </row>
+    <row r="98" spans="1:10" ht="13" hidden="1">
+      <c r="A98" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B98" s="2" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>2021.0</v>
-      </c>
-      <c r="B89" s="2" t="s">
+      <c r="C98"/>
+      <c r="H98" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="I98" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J98" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I89" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J89" s="3" t="s">
+    </row>
+    <row r="99" spans="1:10" ht="13" hidden="1">
+      <c r="A99" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B99" s="2" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>2021.0</v>
-      </c>
-      <c r="B90" s="2" t="s">
+      <c r="C99"/>
+      <c r="H99" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I99" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J99" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="H90" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I90" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J90" s="3" t="s">
+    </row>
+    <row r="100" spans="1:10" ht="13" hidden="1">
+      <c r="A100" s="2">
+        <v>2021</v>
+      </c>
+      <c r="B100" s="2" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>2021.0</v>
-      </c>
-      <c r="B91" s="2" t="s">
+      <c r="C100"/>
+      <c r="H100" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I100" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J100" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I91" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J91" s="3" t="s">
+    </row>
+    <row r="101" spans="1:10" ht="13" hidden="1">
+      <c r="A101" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B101" s="2" t="s">
         <v>272</v>
       </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>2020.0</v>
-      </c>
-      <c r="B92" s="2" t="s">
+      <c r="C101"/>
+      <c r="H101" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I101" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J101" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="H92" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I92" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J92" s="3" t="s">
+    </row>
+    <row r="102" spans="1:10" ht="13" hidden="1">
+      <c r="A102" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B102" s="2" t="s">
         <v>274</v>
       </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>2020.0</v>
-      </c>
-      <c r="B93" s="2" t="s">
+      <c r="C102"/>
+      <c r="H102" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I102" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J102" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="H93" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I93" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J93" s="3" t="s">
+    </row>
+    <row r="103" spans="1:10" ht="13" hidden="1">
+      <c r="A103" s="2">
+        <v>2020</v>
+      </c>
+      <c r="B103" s="2" t="s">
         <v>276</v>
       </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>2020.0</v>
-      </c>
-      <c r="B94" s="2" t="s">
+      <c r="C103"/>
+      <c r="H103" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="I103" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J103" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I94" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B95" s="2" t="s">
+    </row>
+    <row r="104" spans="1:10" ht="13" hidden="1">
+      <c r="A104" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="C95" s="2" t="s">
+      <c r="C104"/>
+      <c r="H104" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I104" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J104" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="I95" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="I96" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J96" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="C97" s="2" t="s">
+    </row>
+    <row r="105" spans="1:10" ht="13" hidden="1">
+      <c r="A105" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="H97" s="3" t="s">
+      <c r="C105"/>
+      <c r="H105" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="I105" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J105" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I97" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I98" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B99" s="2" t="s">
+    </row>
+    <row r="106" spans="1:10" ht="13" hidden="1">
+      <c r="A106" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C99" s="2" t="s">
+      <c r="C106"/>
+      <c r="H106" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="H99" s="3" t="s">
+      <c r="I106" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="J106" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="I99" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J99" s="3" t="s">
+    </row>
+    <row r="107" spans="1:10" ht="13" hidden="1">
+      <c r="A107" s="2">
+        <v>2019</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C107"/>
+      <c r="H107" s="3" t="s">
         <v>292</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="I100" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="I101" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="I102" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2">
-        <v>2019.0</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="I103" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J103" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="I104" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="I105" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="I106" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2">
-        <v>2018.0</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="C107" s="3"/>
-      <c r="H107" s="3" t="s">
-        <v>300</v>
       </c>
       <c r="I107" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J107" s="3" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="108" spans="1:10" ht="13" hidden="1">
       <c r="A108" s="2">
-        <v>2018.0</v>
+        <v>2019</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C108" s="3"/>
+        <v>297</v>
+      </c>
+      <c r="C108"/>
       <c r="H108" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="I108" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J108" s="3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="109" spans="1:10" ht="13" hidden="1">
       <c r="A109" s="2">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="C109" s="3"/>
       <c r="H109" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="I109" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J109" s="3" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="110">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="110" spans="1:10" ht="13" hidden="1">
       <c r="A110" s="2">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>284</v>
-      </c>
+        <v>311</v>
+      </c>
+      <c r="C110" s="3"/>
       <c r="H110" s="3" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="I110" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="111">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="111" spans="1:10" ht="13" hidden="1">
       <c r="A111" s="2">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>322</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="C111"/>
       <c r="H111" s="3" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="I111" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="112">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="112" spans="1:10" ht="13" hidden="1">
       <c r="A112" s="2">
-        <v>2018.0</v>
+        <v>2018</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>324</v>
-      </c>
+        <v>319</v>
+      </c>
+      <c r="C112"/>
       <c r="H112" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I112" s="1" t="b">
         <v>0</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <autoFilter ref="A1:J112" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="2">
+      <filters>
+        <filter val="10"/>
+        <filter val="7.5"/>
+        <filter val="8"/>
+        <filter val="8.5"/>
+        <filter val="9"/>
+        <filter val="9.5"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="8">
+      <filters>
+        <filter val="TRUE"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A6:J64">
+      <sortCondition descending="1" ref="C1:C112"/>
+    </sortState>
+  </autoFilter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>